--- a/The structure and semantics of the website/Семантическое ядро Сайт АБС.xlsx
+++ b/The structure and semantics of the website/Семантическое ядро Сайт АБС.xlsx
@@ -32,6 +32,9 @@
     <sheet name="машинист автовышки и автогидроп" sheetId="17" r:id="rId17"/>
     <sheet name="Справка" sheetId="19" r:id="rId18"/>
     <sheet name="водители категории B" sheetId="20" r:id="rId19"/>
+    <sheet name="моторист цементировочного агр" sheetId="21" r:id="rId121"/>
+    <sheet name="слесарь по ремонту ДСТ" sheetId="22" r:id="rId122"/>
+    <sheet name="Слесари" sheetId="23" r:id="rId123"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2128,10 +2131,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2159,8 +2167,66 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2172,8 +2238,49 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -2182,12 +2289,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -2222,6 +2333,86 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="4"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="3" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="6"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2581,6 +2772,27 @@
 </table>
 </file>
 
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="CementingMotoristKeywords" displayName="CementingMotoristKeywords" ref="A2:M9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="Фраза"/>
+    <x:tableColumn id="2" name="Дата сбора"/>
+    <x:tableColumn id="3" name="База [Bukvarix]"/>
+    <x:tableColumn id="4" name="Точная [Bukvarix]"/>
+    <x:tableColumn id="5" name="Регион"/>
+    <x:tableColumn id="6" name="Источник"/>
+    <x:tableColumn id="7" name="URL источника"/>
+    <x:tableColumn id="8" name="Интент"/>
+    <x:tableColumn id="9" name="Происхождение"/>
+    <x:tableColumn id="10" name="Статус частотности"/>
+    <x:tableColumn id="11" name="Маска-источник"/>
+    <x:tableColumn id="12" name="URL страницы"/>
+    <x:tableColumn id="13" name="Решение"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A2:G67" totalsRowShown="0" headerRowCellStyle="Normal">
   <autoFilter ref="A2:G67" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
@@ -2595,6 +2807,48 @@
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="DSTMechanicKeywords" displayName="DSTMechanicKeywords" ref="A2:M10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="Фраза"/>
+    <x:tableColumn id="2" name="Дата сбора"/>
+    <x:tableColumn id="3" name="База [Bukvarix]"/>
+    <x:tableColumn id="4" name="Точная [Bukvarix]"/>
+    <x:tableColumn id="5" name="Регион"/>
+    <x:tableColumn id="6" name="Источник"/>
+    <x:tableColumn id="7" name="URL источника"/>
+    <x:tableColumn id="8" name="Интент"/>
+    <x:tableColumn id="9" name="Происхождение"/>
+    <x:tableColumn id="10" name="Статус частотности"/>
+    <x:tableColumn id="11" name="Маска-источник"/>
+    <x:tableColumn id="12" name="URL страницы"/>
+    <x:tableColumn id="13" name="Решение"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="LocksmithCategoryKeywords" displayName="LocksmithCategoryKeywords" ref="A2:M9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="Фраза"/>
+    <x:tableColumn id="2" name="Дата сбора"/>
+    <x:tableColumn id="3" name="База [Bukvarix]"/>
+    <x:tableColumn id="4" name="Точная [Bukvarix]"/>
+    <x:tableColumn id="5" name="Регион"/>
+    <x:tableColumn id="6" name="Источник"/>
+    <x:tableColumn id="7" name="URL источника"/>
+    <x:tableColumn id="8" name="Интент"/>
+    <x:tableColumn id="9" name="Происхождение"/>
+    <x:tableColumn id="10" name="Статус частотности"/>
+    <x:tableColumn id="11" name="Маска-источник"/>
+    <x:tableColumn id="12" name="URL страницы"/>
+    <x:tableColumn id="13" name="Решение"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3355,6 +3609,16 @@
       <c r="T17" s="9"/>
       <c r="U17" s="9"/>
     </row>
+    <row r="18">
+      <c r="D18" s="9" t="str">
+        <v>моторист цементировочного агр</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" s="9" t="str">
+        <v>слесарь по ремонту ДСТ</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="B1:U1"/>
@@ -11991,6 +12255,1089 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:dimension ref="A1:M9"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="51" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="39" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="45" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="34"/>
+      <x:c r="D1" s="34"/>
+      <x:c r="E1" s="34"/>
+      <x:c r="F1" s="34"/>
+      <x:c r="G1" s="34"/>
+      <x:c r="H1" s="34"/>
+      <x:c r="I1" s="34"/>
+      <x:c r="J1" s="34"/>
+      <x:c r="K1" s="34"/>
+      <x:c r="L1" s="34"/>
+      <x:c r="M1" s="34"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>Фраза</x:v>
+      </x:c>
+      <x:c r="B2" s="39" t="str">
+        <x:v>Дата сбора</x:v>
+      </x:c>
+      <x:c r="C2" s="39" t="str">
+        <x:v>База [Bukvarix]</x:v>
+      </x:c>
+      <x:c r="D2" s="39" t="str">
+        <x:v>Точная [Bukvarix]</x:v>
+      </x:c>
+      <x:c r="E2" s="39" t="str">
+        <x:v>Регион</x:v>
+      </x:c>
+      <x:c r="F2" s="39" t="str">
+        <x:v>Источник</x:v>
+      </x:c>
+      <x:c r="G2" s="39" t="str">
+        <x:v>URL источника</x:v>
+      </x:c>
+      <x:c r="H2" s="39" t="str">
+        <x:v>Интент</x:v>
+      </x:c>
+      <x:c r="I2" s="39" t="str">
+        <x:v>Происхождение</x:v>
+      </x:c>
+      <x:c r="J2" s="39" t="str">
+        <x:v>Статус частотности</x:v>
+      </x:c>
+      <x:c r="K2" s="39" t="str">
+        <x:v>Маска-источник</x:v>
+      </x:c>
+      <x:c r="L2" s="39" t="str">
+        <x:v>URL страницы</x:v>
+      </x:c>
+      <x:c r="M2" s="39" t="str">
+        <x:v>Решение</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="60" customHeight="1">
+      <x:c r="A3" s="41" t="str">
+        <x:v>подбор моториста цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="B3" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C3" s="43"/>
+      <x:c r="D3" s="43"/>
+      <x:c r="E3" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F3" s="41" t="str">
+        <x:v>HEAAD</x:v>
+      </x:c>
+      <x:c r="G3" s="41" t="str">
+        <x:v>https://heaad.ru/poisk-i-podbor-personala/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="H3" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I3" s="41" t="str">
+        <x:v>Фраза на странице конкурента</x:v>
+      </x:c>
+      <x:c r="J3" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K3" s="41" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="L3" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="M3" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
+      <x:c r="A4" s="41" t="str">
+        <x:v>отбор мотористов цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="B4" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C4" s="43"/>
+      <x:c r="D4" s="43"/>
+      <x:c r="E4" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F4" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G4" s="41"/>
+      <x:c r="H4" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I4" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J4" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K4" s="41" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="L4" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="M4" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="60" customHeight="1">
+      <x:c r="A5" s="41" t="str">
+        <x:v>аутстаффинг мотористов цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="B5" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C5" s="43"/>
+      <x:c r="D5" s="43"/>
+      <x:c r="E5" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F5" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G5" s="41"/>
+      <x:c r="H5" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I5" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J5" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K5" s="41" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="L5" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="M5" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="41" t="str">
+        <x:v>предоставление мотористов цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="B6" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C6" s="43"/>
+      <x:c r="D6" s="43"/>
+      <x:c r="E6" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F6" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G6" s="41"/>
+      <x:c r="H6" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I6" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J6" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K6" s="41" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="L6" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="M6" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
+      <x:c r="A7" s="41" t="str">
+        <x:v>аренда персонала моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="B7" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C7" s="43"/>
+      <x:c r="D7" s="43"/>
+      <x:c r="E7" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F7" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G7" s="41"/>
+      <x:c r="H7" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I7" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J7" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K7" s="41" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="L7" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="M7" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="60" customHeight="1">
+      <x:c r="A8" s="41" t="str">
+        <x:v>моторист ЦА персонал на объект</x:v>
+      </x:c>
+      <x:c r="B8" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C8" s="43"/>
+      <x:c r="D8" s="43"/>
+      <x:c r="E8" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F8" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G8" s="41"/>
+      <x:c r="H8" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I8" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J8" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K8" s="41" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="L8" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="M8" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="60" customHeight="1">
+      <x:c r="A9" s="41" t="str">
+        <x:v>ищу моториста цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="B9" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C9" s="43" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D9" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="41" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F9" s="41" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G9" s="41" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%9C%D0%BE%D1%82%D0%BE%D1%80%D0%B8%D1%81%D1%82%20%D1%86%D0%B5%D0%BC%D0%B5%D0%BD%D1%82%D0%B8%D1%80%D0%BE%D0%B2%D0%BE%D1%87%D0%BD%D0%BE%D0%B3%D0%BE%20%D0%B0%D0%B3%D1%80%D0%B5%D0%B3%D0%B0%D1%82%D0%B0</x:v>
+      </x:c>
+      <x:c r="H9" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I9" s="41" t="str">
+        <x:v>Фраза и частотности из CSV Bukvarix</x:v>
+      </x:c>
+      <x:c r="J9" s="41" t="str">
+        <x:v>Проверено 22.10.2026; дата базы не указана</x:v>
+      </x:c>
+      <x:c r="K9" s="41" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="L9" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="M9" s="41" t="str">
+        <x:v>Оставить: ищет специалиста; не считать точный B2B-спрос подтверждённым</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0ede5fb156f458a"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:dimension ref="A1:M10"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="51" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="39" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="45" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="34"/>
+      <x:c r="D1" s="34"/>
+      <x:c r="E1" s="34"/>
+      <x:c r="F1" s="34"/>
+      <x:c r="G1" s="34"/>
+      <x:c r="H1" s="34"/>
+      <x:c r="I1" s="34"/>
+      <x:c r="J1" s="34"/>
+      <x:c r="K1" s="34"/>
+      <x:c r="L1" s="34"/>
+      <x:c r="M1" s="34"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>Фраза</x:v>
+      </x:c>
+      <x:c r="B2" s="39" t="str">
+        <x:v>Дата сбора</x:v>
+      </x:c>
+      <x:c r="C2" s="39" t="str">
+        <x:v>База [Bukvarix]</x:v>
+      </x:c>
+      <x:c r="D2" s="39" t="str">
+        <x:v>Точная [Bukvarix]</x:v>
+      </x:c>
+      <x:c r="E2" s="39" t="str">
+        <x:v>Регион</x:v>
+      </x:c>
+      <x:c r="F2" s="39" t="str">
+        <x:v>Источник</x:v>
+      </x:c>
+      <x:c r="G2" s="39" t="str">
+        <x:v>URL источника</x:v>
+      </x:c>
+      <x:c r="H2" s="39" t="str">
+        <x:v>Интент</x:v>
+      </x:c>
+      <x:c r="I2" s="39" t="str">
+        <x:v>Происхождение</x:v>
+      </x:c>
+      <x:c r="J2" s="39" t="str">
+        <x:v>Статус частотности</x:v>
+      </x:c>
+      <x:c r="K2" s="39" t="str">
+        <x:v>Маска-источник</x:v>
+      </x:c>
+      <x:c r="L2" s="39" t="str">
+        <x:v>URL страницы</x:v>
+      </x:c>
+      <x:c r="M2" s="39" t="str">
+        <x:v>Решение</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="60" customHeight="1">
+      <x:c r="A3" s="41" t="str">
+        <x:v>подбор слесаря по ремонту дорожно-строительной техники и тракторов</x:v>
+      </x:c>
+      <x:c r="B3" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C3" s="43"/>
+      <x:c r="D3" s="43"/>
+      <x:c r="E3" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F3" s="41" t="str">
+        <x:v>HEAAD</x:v>
+      </x:c>
+      <x:c r="G3" s="41" t="str">
+        <x:v>https://heaad.ru/poisk-i-podbor-personala/slesar-po-remontu-dorozhno-stroitelnoi-tekhniki-i-traktorov/</x:v>
+      </x:c>
+      <x:c r="H3" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I3" s="41" t="str">
+        <x:v>Фраза на странице конкурента</x:v>
+      </x:c>
+      <x:c r="J3" s="41" t="str">
+        <x:v>Не проверялась</x:v>
+      </x:c>
+      <x:c r="K3" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L3" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M3" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
+      <x:c r="A4" s="41" t="str">
+        <x:v>найти слесаря по ремонту техники</x:v>
+      </x:c>
+      <x:c r="B4" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C4" s="43"/>
+      <x:c r="D4" s="43"/>
+      <x:c r="E4" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F4" s="41" t="str">
+        <x:v>HEAAD</x:v>
+      </x:c>
+      <x:c r="G4" s="41" t="str">
+        <x:v>https://heaad.ru/poisk-i-podbor-personala/slesar-po-remontu-dorozhno-stroitelnoi-tekhniki-i-traktorov/</x:v>
+      </x:c>
+      <x:c r="H4" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I4" s="41" t="str">
+        <x:v>Фраза на странице конкурента</x:v>
+      </x:c>
+      <x:c r="J4" s="41" t="str">
+        <x:v>Не проверялась</x:v>
+      </x:c>
+      <x:c r="K4" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L4" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M4" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="60" customHeight="1">
+      <x:c r="A5" s="41" t="str">
+        <x:v>подбор и найм слесаря по ремонту дорожно-строительной техники</x:v>
+      </x:c>
+      <x:c r="B5" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C5" s="43"/>
+      <x:c r="D5" s="43"/>
+      <x:c r="E5" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F5" s="41" t="str">
+        <x:v>UP business</x:v>
+      </x:c>
+      <x:c r="G5" s="41" t="str">
+        <x:v>https://upinc.ru/podbor/avtoservis/slesar-remontu-dorozhno-stroitelnoj-tekhniki/</x:v>
+      </x:c>
+      <x:c r="H5" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I5" s="41" t="str">
+        <x:v>Нормализована грамматика заголовка</x:v>
+      </x:c>
+      <x:c r="J5" s="41" t="str">
+        <x:v>Не проверялась</x:v>
+      </x:c>
+      <x:c r="K5" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L5" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M5" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="41" t="str">
+        <x:v>отбор слесарей по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="B6" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C6" s="43"/>
+      <x:c r="D6" s="43"/>
+      <x:c r="E6" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F6" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G6" s="41"/>
+      <x:c r="H6" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I6" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J6" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K6" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L6" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M6" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
+      <x:c r="A7" s="41" t="str">
+        <x:v>аутстаффинг слесарей по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="B7" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C7" s="43"/>
+      <x:c r="D7" s="43"/>
+      <x:c r="E7" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F7" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G7" s="41"/>
+      <x:c r="H7" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I7" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J7" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K7" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L7" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M7" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="60" customHeight="1">
+      <x:c r="A8" s="41" t="str">
+        <x:v>предоставление слесарей по ремонту спецтехники</x:v>
+      </x:c>
+      <x:c r="B8" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C8" s="43"/>
+      <x:c r="D8" s="43"/>
+      <x:c r="E8" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F8" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G8" s="41"/>
+      <x:c r="H8" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I8" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J8" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K8" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L8" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M8" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="60" customHeight="1">
+      <x:c r="A9" s="41" t="str">
+        <x:v>аренда персонала слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="B9" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C9" s="43"/>
+      <x:c r="D9" s="43"/>
+      <x:c r="E9" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F9" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G9" s="41"/>
+      <x:c r="H9" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I9" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J9" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K9" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L9" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M9" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="60" customHeight="1">
+      <x:c r="A10" s="41" t="str">
+        <x:v>слесари по ремонту дорожно-строительной техники для компаний</x:v>
+      </x:c>
+      <x:c r="B10" s="42" t="n">
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="C10" s="43"/>
+      <x:c r="D10" s="43"/>
+      <x:c r="E10" s="41" t="str">
+        <x:v>Россия</x:v>
+      </x:c>
+      <x:c r="F10" s="41" t="str">
+        <x:v>Маска по конкурентной тематике</x:v>
+      </x:c>
+      <x:c r="G10" s="41"/>
+      <x:c r="H10" s="41" t="str">
+        <x:v>Поиск / предоставление специалистов</x:v>
+      </x:c>
+      <x:c r="I10" s="41" t="str">
+        <x:v>Синтезированная маска, не найденный запрос</x:v>
+      </x:c>
+      <x:c r="J10" s="41" t="str">
+        <x:v>В базе Bukvarix ключ не найден; частотность неизвестна</x:v>
+      </x:c>
+      <x:c r="K10" s="41" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="L10" s="41" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="M10" s="41" t="str">
+        <x:v>Оставить как коммерческую формулировку; частотность не подтверждена</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b24c64cc224d38"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="44" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="32" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="49" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Слесари — коммерческое ядро /slesari/</x:v>
+      </x:c>
+      <x:c r="B1" s="45"/>
+      <x:c r="C1" s="45"/>
+      <x:c r="D1" s="45"/>
+      <x:c r="E1" s="45"/>
+      <x:c r="F1" s="45"/>
+      <x:c r="G1" s="45"/>
+      <x:c r="H1" s="45"/>
+      <x:c r="I1" s="45"/>
+      <x:c r="J1" s="45"/>
+      <x:c r="K1" s="45"/>
+      <x:c r="L1" s="45"/>
+      <x:c r="M1" s="45"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="50" t="str">
+        <x:v>Фраза</x:v>
+      </x:c>
+      <x:c r="B2" s="50" t="str">
+        <x:v>Дата сбора</x:v>
+      </x:c>
+      <x:c r="C2" s="50" t="str">
+        <x:v>База [Bukvarix]</x:v>
+      </x:c>
+      <x:c r="D2" s="50" t="str">
+        <x:v>Точная [Bukvarix]</x:v>
+      </x:c>
+      <x:c r="E2" s="50" t="str">
+        <x:v>Регион</x:v>
+      </x:c>
+      <x:c r="F2" s="50" t="str">
+        <x:v>Источник</x:v>
+      </x:c>
+      <x:c r="G2" s="50" t="str">
+        <x:v>URL источника</x:v>
+      </x:c>
+      <x:c r="H2" s="50" t="str">
+        <x:v>Интент</x:v>
+      </x:c>
+      <x:c r="I2" s="50" t="str">
+        <x:v>Происхождение</x:v>
+      </x:c>
+      <x:c r="J2" s="50" t="str">
+        <x:v>Статус частотности</x:v>
+      </x:c>
+      <x:c r="K2" s="50" t="str">
+        <x:v>Маска-источник</x:v>
+      </x:c>
+      <x:c r="L2" s="50" t="str">
+        <x:v>URL страницы</x:v>
+      </x:c>
+      <x:c r="M2" s="50" t="str">
+        <x:v>Решение</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="84" customHeight="1">
+      <x:c r="A3" s="52" t="str">
+        <x:v>аутсорсинг слесарь</x:v>
+      </x:c>
+      <x:c r="B3" s="53" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="C3" s="54" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%B0%D1%83%D1%82%D1%81%D0%BE%D1%80%D1%81%D0%B8%D0%BD%D0%B3%20%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D0%B5%D0%B9</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="str">
+        <x:v>Коммерческий поиск специалиста</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="str">
+        <x:v>Найденный запрос Bukvarix</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="str">
+        <x:v>Проверена; дата базы неизвестна</x:v>
+      </x:c>
+      <x:c r="K3" s="52" t="str">
+        <x:v>аутсорсинг слесарей</x:v>
+      </x:c>
+      <x:c r="L3" s="52" t="str">
+        <x:v>/slesari/</x:v>
+      </x:c>
+      <x:c r="M3" s="52" t="str">
+        <x:v>Общий запрос слесарей; не присваивать только спецтехнике</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="84" customHeight="1">
+      <x:c r="A4" s="52" t="str">
+        <x:v>аутсорсинг слесарей</x:v>
+      </x:c>
+      <x:c r="B4" s="53" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="C4" s="54" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D4" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%B0%D1%83%D1%82%D1%81%D0%BE%D1%80%D1%81%D0%B8%D0%BD%D0%B3%20%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D0%B5%D0%B9</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="str">
+        <x:v>Коммерческий поиск специалиста</x:v>
+      </x:c>
+      <x:c r="I4" s="52" t="str">
+        <x:v>Найденный запрос Bukvarix</x:v>
+      </x:c>
+      <x:c r="J4" s="52" t="str">
+        <x:v>Проверена; дата базы неизвестна</x:v>
+      </x:c>
+      <x:c r="K4" s="52" t="str">
+        <x:v>аутсорсинг слесарей</x:v>
+      </x:c>
+      <x:c r="L4" s="52" t="str">
+        <x:v>/slesari/</x:v>
+      </x:c>
+      <x:c r="M4" s="52" t="str">
+        <x:v>Общий запрос слесарей; не присваивать только спецтехнике</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="84" customHeight="1">
+      <x:c r="A5" s="52" t="str">
+        <x:v>слесарь аутсорсинг</x:v>
+      </x:c>
+      <x:c r="B5" s="53" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="C5" s="54" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D5" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%B0%D1%83%D1%82%D1%81%D0%BE%D1%80%D1%81%D0%B8%D0%BD%D0%B3%20%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D0%B5%D0%B9</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="str">
+        <x:v>Коммерческий поиск специалиста</x:v>
+      </x:c>
+      <x:c r="I5" s="52" t="str">
+        <x:v>Найденный запрос Bukvarix</x:v>
+      </x:c>
+      <x:c r="J5" s="52" t="str">
+        <x:v>Проверена; дата базы неизвестна</x:v>
+      </x:c>
+      <x:c r="K5" s="52" t="str">
+        <x:v>аутсорсинг слесарей</x:v>
+      </x:c>
+      <x:c r="L5" s="52" t="str">
+        <x:v>/slesari/</x:v>
+      </x:c>
+      <x:c r="M5" s="52" t="str">
+        <x:v>Общий запрос слесарей; не присваивать только спецтехнике</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="84" customHeight="1">
+      <x:c r="A6" s="52" t="str">
+        <x:v>подбор персонала слесарей</x:v>
+      </x:c>
+      <x:c r="B6" s="53" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="C6" s="54" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D6" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%BF%D0%BE%D0%B4%D0%B1%D0%BE%D1%80%20%D0%BF%D0%B5%D1%80%D1%81%D0%BE%D0%BD%D0%B0%D0%BB%D0%B0%20%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D0%B5%D0%B9</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="str">
+        <x:v>Коммерческий поиск специалиста</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="str">
+        <x:v>Найденный запрос Bukvarix</x:v>
+      </x:c>
+      <x:c r="J6" s="52" t="str">
+        <x:v>Проверена; дата базы неизвестна</x:v>
+      </x:c>
+      <x:c r="K6" s="52" t="str">
+        <x:v>подбор персонала слесарей</x:v>
+      </x:c>
+      <x:c r="L6" s="52" t="str">
+        <x:v>/slesari/</x:v>
+      </x:c>
+      <x:c r="M6" s="52" t="str">
+        <x:v>Общий запрос слесарей; не присваивать только спецтехнике</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="84" customHeight="1">
+      <x:c r="A7" s="52" t="str">
+        <x:v>подбор слесаря</x:v>
+      </x:c>
+      <x:c r="B7" s="53" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="C7" s="54" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D7" s="54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%BF%D0%BE%D0%B4%D0%B1%D0%BE%D1%80%20%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D0%B5%D0%B9</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="str">
+        <x:v>Коммерческий поиск специалиста</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="str">
+        <x:v>Найденный запрос Bukvarix</x:v>
+      </x:c>
+      <x:c r="J7" s="52" t="str">
+        <x:v>Проверена; дата базы неизвестна</x:v>
+      </x:c>
+      <x:c r="K7" s="52" t="str">
+        <x:v>подбор слесарей</x:v>
+      </x:c>
+      <x:c r="L7" s="52" t="str">
+        <x:v>/slesari/</x:v>
+      </x:c>
+      <x:c r="M7" s="52" t="str">
+        <x:v>Общий запрос слесарей; не присваивать только спецтехнике</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="84" customHeight="1">
+      <x:c r="A8" s="52" t="str">
+        <x:v>подбор слесарей</x:v>
+      </x:c>
+      <x:c r="B8" s="53" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="C8" s="54" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D8" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="52" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F8" s="52" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%BF%D0%BE%D0%B4%D0%B1%D0%BE%D1%80%20%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D0%B5%D0%B9</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="str">
+        <x:v>Коммерческий поиск специалиста</x:v>
+      </x:c>
+      <x:c r="I8" s="52" t="str">
+        <x:v>Найденный запрос Bukvarix</x:v>
+      </x:c>
+      <x:c r="J8" s="52" t="str">
+        <x:v>Проверена; дата базы неизвестна</x:v>
+      </x:c>
+      <x:c r="K8" s="52" t="str">
+        <x:v>подбор слесарей</x:v>
+      </x:c>
+      <x:c r="L8" s="52" t="str">
+        <x:v>/slesari/</x:v>
+      </x:c>
+      <x:c r="M8" s="52" t="str">
+        <x:v>Общий запрос слесарей; не присваивать только спецтехнике</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="84" customHeight="1">
+      <x:c r="A9" s="52" t="str">
+        <x:v>слесарь подбор</x:v>
+      </x:c>
+      <x:c r="B9" s="53" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="C9" s="54" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D9" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="52" t="str">
+        <x:v>Весь мир</x:v>
+      </x:c>
+      <x:c r="F9" s="52" t="str">
+        <x:v>Bukvarix</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="str">
+        <x:v>https://www.bukvarix.com/keywords/?q=%D0%BF%D0%BE%D0%B4%D0%B1%D0%BE%D1%80%20%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D0%B5%D0%B9</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="str">
+        <x:v>Коммерческий поиск специалиста</x:v>
+      </x:c>
+      <x:c r="I9" s="52" t="str">
+        <x:v>Найденный запрос Bukvarix</x:v>
+      </x:c>
+      <x:c r="J9" s="52" t="str">
+        <x:v>Проверена; дата базы неизвестна</x:v>
+      </x:c>
+      <x:c r="K9" s="52" t="str">
+        <x:v>подбор слесарей</x:v>
+      </x:c>
+      <x:c r="L9" s="52" t="str">
+        <x:v>/slesari/</x:v>
+      </x:c>
+      <x:c r="M9" s="52" t="str">
+        <x:v>Общий запрос слесарей; не присваивать только спецтехнике</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11a84f9070bd445b"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G67"/>
